--- a/49847_Intercuenca_Medio_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_4127_completo.xlsx
+++ b/49847_Intercuenca_Medio_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_4127_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R1b20d4b4a7f24483"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5dce6c846c674fc1"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/49847_Intercuenca_Medio_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_4127_completo.xlsx
+++ b/49847_Intercuenca_Medio_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_4127_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5dce6c846c674fc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R4a933d69cdfb42e5"/>
   </x:sheets>
 </x:workbook>
 </file>
